--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>92.54474014061059</v>
+        <v>92.54408824327614</v>
       </c>
       <c r="C2">
-        <v>129.0964412588058</v>
+        <v>128.7919888474937</v>
       </c>
       <c r="D2">
-        <v>146.6242510942771</v>
+        <v>146.3427044212414</v>
       </c>
       <c r="E2">
-        <v>156.5066480009596</v>
+        <v>156.475498564193</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>112.1916836622431</v>
+        <v>112.1909169624402</v>
       </c>
       <c r="C3">
-        <v>154.9434366247717</v>
+        <v>154.6121699330905</v>
       </c>
       <c r="D3">
-        <v>173.433670369002</v>
+        <v>173.0581761789361</v>
       </c>
       <c r="E3">
-        <v>186.0785908418733</v>
+        <v>186.0312335155923</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>99.47381076266858</v>
+        <v>99.47308481930261</v>
       </c>
       <c r="C4">
-        <v>142.9947996633675</v>
+        <v>142.7292489249972</v>
       </c>
       <c r="D4">
-        <v>164.313419391844</v>
+        <v>163.9964539952161</v>
       </c>
       <c r="E4">
-        <v>177.7366062292226</v>
+        <v>177.6900285233762</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>77.80979140863415</v>
+        <v>77.8092834810536</v>
       </c>
       <c r="C5">
-        <v>105.4281917505071</v>
+        <v>104.9565473105472</v>
       </c>
       <c r="D5">
-        <v>114.5867636320345</v>
+        <v>114.2750639760141</v>
       </c>
       <c r="E5">
-        <v>123.7547408475159</v>
+        <v>123.7067404508027</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>68.39841216087127</v>
+        <v>68.39796236781282</v>
       </c>
       <c r="C6">
-        <v>92.45609996066413</v>
+        <v>92.04576915324967</v>
       </c>
       <c r="D6">
-        <v>101.4896934151635</v>
+        <v>101.2143022711683</v>
       </c>
       <c r="E6">
-        <v>108.2814980734355</v>
+        <v>108.2396194310451</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7.359724896928105</v>
+        <v>7.359677613378202</v>
       </c>
       <c r="C7">
-        <v>9.824192548335123</v>
+        <v>9.779775600702974</v>
       </c>
       <c r="D7">
-        <v>10.80288259483659</v>
+        <v>10.77330310742233</v>
       </c>
       <c r="E7">
-        <v>11.46647658683863</v>
+        <v>11.46206920959787</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>349.2498139190442</v>
+        <v>349.2472554799686</v>
       </c>
       <c r="C8">
-        <v>491.2396518468012</v>
+        <v>494.1267385276846</v>
       </c>
       <c r="D8">
-        <v>568.8485080698634</v>
+        <v>571.1892748000021</v>
       </c>
       <c r="E8">
-        <v>611.5977192606124</v>
+        <v>611.9221957421374</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>99.90058556864138</v>
+        <v>99.89993426935246</v>
       </c>
       <c r="C9">
-        <v>134.5045581053082</v>
+        <v>134.0014750840556</v>
       </c>
       <c r="D9">
-        <v>147.7896822886859</v>
+        <v>147.4063309106015</v>
       </c>
       <c r="E9">
-        <v>157.8957700449844</v>
+        <v>157.838183776268</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>43.05038409831338</v>
+        <v>43.05011326026328</v>
       </c>
       <c r="C10">
-        <v>56.39092900553602</v>
+        <v>56.13757546219063</v>
       </c>
       <c r="D10">
-        <v>62.5722401152523</v>
+        <v>62.40616809931717</v>
       </c>
       <c r="E10">
-        <v>65.60043381073375</v>
+        <v>65.57972984383662</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.910677975125875</v>
+        <v>7.91312554259856</v>
       </c>
       <c r="C11">
-        <v>9.840885596036706</v>
+        <v>9.798670396509774</v>
       </c>
       <c r="D11">
-        <v>10.79791207364155</v>
+        <v>10.76982854540284</v>
       </c>
       <c r="E11">
-        <v>12.21472371348436</v>
+        <v>12.21110437642865</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>18.91319039043179</v>
+        <v>18.91752529032662</v>
       </c>
       <c r="C12">
-        <v>25.85986069295708</v>
+        <v>25.7422526100852</v>
       </c>
       <c r="D12">
-        <v>28.5411552733841</v>
+        <v>28.46237494598668</v>
       </c>
       <c r="E12">
-        <v>29.52913802988394</v>
+        <v>29.51783833593317</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>24.19718501648777</v>
+        <v>24.19703267022695</v>
       </c>
       <c r="C13">
-        <v>31.42095294690973</v>
+        <v>31.27778814939301</v>
       </c>
       <c r="D13">
-        <v>35.19982168201505</v>
+        <v>35.10601874869108</v>
       </c>
       <c r="E13">
-        <v>37.33765456045538</v>
+        <v>37.32575823078887</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>92.54408824327614</v>
+        <v>3.542357444718704</v>
       </c>
       <c r="C2">
-        <v>128.7919888474937</v>
+        <v>10.47590339907844</v>
       </c>
       <c r="D2">
-        <v>146.3427044212414</v>
+        <v>23.10674280335391</v>
       </c>
       <c r="E2">
-        <v>156.475498564193</v>
+        <v>37.61430253946948</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>112.1909169624402</v>
+        <v>37.54961302416367</v>
       </c>
       <c r="C3">
-        <v>154.6121699330905</v>
+        <v>95.53272288548679</v>
       </c>
       <c r="D3">
-        <v>173.0581761789361</v>
+        <v>129.9702221098949</v>
       </c>
       <c r="E3">
-        <v>186.0312335155923</v>
+        <v>155.0260279296602</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>99.47308481930261</v>
+        <v>3.777458917188707</v>
       </c>
       <c r="C4">
-        <v>142.7292489249972</v>
+        <v>10.19494635178551</v>
       </c>
       <c r="D4">
-        <v>163.9964539952161</v>
+        <v>18.68314032856892</v>
       </c>
       <c r="E4">
-        <v>177.6900285233762</v>
+        <v>26.13088654755533</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>77.8092834810536</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>104.9565473105472</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>114.2750639760141</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>123.7067404508027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>68.39796236781282</v>
+        <v>22.95875659898612</v>
       </c>
       <c r="C6">
-        <v>92.04576915324967</v>
+        <v>39.26427914928832</v>
       </c>
       <c r="D6">
-        <v>101.2143022711683</v>
+        <v>39.6363701201778</v>
       </c>
       <c r="E6">
-        <v>108.2396194310451</v>
+        <v>35.06353868893011</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7.359677613378202</v>
+        <v>2.453225871126067</v>
       </c>
       <c r="C7">
-        <v>9.779775600702974</v>
+        <v>6.51985040046865</v>
       </c>
       <c r="D7">
-        <v>10.77330310742233</v>
+        <v>7.900422278776373</v>
       </c>
       <c r="E7">
-        <v>11.46206920959787</v>
+        <v>9.169655367678295</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>349.2472554799686</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>494.1267385276846</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>571.1892748000021</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>611.9221957421374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>99.89993426935246</v>
+        <v>179.4319207750505</v>
       </c>
       <c r="C9">
-        <v>134.0014750840556</v>
+        <v>383.8786218591544</v>
       </c>
       <c r="D9">
-        <v>147.4063309106015</v>
+        <v>573.8828999529244</v>
       </c>
       <c r="E9">
-        <v>157.838183776268</v>
+        <v>754.8782702343253</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>43.05011326026328</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>56.13757546219063</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>62.40616809931717</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>65.57972984383662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>7.91312554259856</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>9.798670396509774</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>10.76982854540284</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>12.21110437642865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>18.91752529032662</v>
+        <v>232.3460157452936</v>
       </c>
       <c r="C12">
-        <v>25.7422526100852</v>
+        <v>343.6590723446374</v>
       </c>
       <c r="D12">
-        <v>28.46237494598668</v>
+        <v>321.6248368896494</v>
       </c>
       <c r="E12">
-        <v>29.51783833593317</v>
+        <v>257.3350008773661</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>24.19703267022695</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>31.27778814939301</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>35.10601874869108</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>37.32575823078887</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.542357444718704</v>
+        <v>11.96977428775308</v>
       </c>
       <c r="C2">
-        <v>10.47590339907844</v>
+        <v>16.65812550362794</v>
       </c>
       <c r="D2">
-        <v>23.10674280335391</v>
+        <v>18.9281581766396</v>
       </c>
       <c r="E2">
-        <v>37.61430253946948</v>
+        <v>20.23874711968005</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>37.54961302416367</v>
+        <v>71.17611127046872</v>
       </c>
       <c r="C3">
-        <v>95.53272288548679</v>
+        <v>98.08898357262257</v>
       </c>
       <c r="D3">
-        <v>129.9702221098949</v>
+        <v>109.791490590099</v>
       </c>
       <c r="E3">
-        <v>155.0260279296602</v>
+        <v>118.0218518128452</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.777458917188707</v>
+        <v>9.214348909577508</v>
       </c>
       <c r="C4">
-        <v>10.19494635178551</v>
+        <v>13.22123568989447</v>
       </c>
       <c r="D4">
-        <v>18.68314032856892</v>
+        <v>15.19125047534633</v>
       </c>
       <c r="E4">
-        <v>26.13088654755533</v>
+        <v>16.45970790532327</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22.95875659898612</v>
+        <v>25.2749037821515</v>
       </c>
       <c r="C6">
-        <v>39.26427914928832</v>
+        <v>34.01341031757563</v>
       </c>
       <c r="D6">
-        <v>39.6363701201778</v>
+        <v>37.40143218776973</v>
       </c>
       <c r="E6">
-        <v>35.06353868893011</v>
+        <v>39.99747758310072</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.453225871126067</v>
+        <v>4.661129155139528</v>
       </c>
       <c r="C7">
-        <v>6.51985040046865</v>
+        <v>6.193857880445217</v>
       </c>
       <c r="D7">
-        <v>7.900422278776373</v>
+        <v>6.823091968034138</v>
       </c>
       <c r="E7">
-        <v>9.169655367678295</v>
+        <v>7.259310499411985</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>179.4319207750505</v>
+        <v>333.201354615092</v>
       </c>
       <c r="C9">
-        <v>383.8786218591544</v>
+        <v>446.9419659280547</v>
       </c>
       <c r="D9">
-        <v>573.8828999529244</v>
+        <v>491.6518664148999</v>
       </c>
       <c r="E9">
-        <v>754.8782702343253</v>
+        <v>526.445758236826</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>232.3460157452936</v>
+        <v>216.114766766073</v>
       </c>
       <c r="C12">
-        <v>343.6590723446374</v>
+        <v>294.0807972228088</v>
       </c>
       <c r="D12">
-        <v>321.6248368896494</v>
+        <v>325.1556125158604</v>
       </c>
       <c r="E12">
-        <v>257.3350008773661</v>
+        <v>337.2132797237934</v>
       </c>
     </row>
     <row r="13" spans="1:5">
